--- a/fixtures/idea_exports/Duplicate.xlsx
+++ b/fixtures/idea_exports/Duplicate.xlsx
@@ -476,82 +476,82 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>990</v>
+        <v>598</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45677</v>
+        <v>45670</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Rent Expense</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9383.719999999999</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1262.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1066</v>
+        <v>672</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45677</v>
+        <v>45670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Rent Expense</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9383.719999999999</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1262.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1468</v>
+        <v>961</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45685</v>
+        <v>45674</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -561,16 +561,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1013.26</v>
+        <v>1551.72</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -578,14 +578,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1550</v>
+        <v>979</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45685</v>
+        <v>45674</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -595,16 +595,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1013.26</v>
+        <v>1551.72</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -612,19 +612,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1844</v>
+        <v>2102</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45691</v>
+        <v>45695</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>VAT Payable</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2634.21</v>
+        <v>3113.62</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -646,33 +646,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1873</v>
+        <v>2147</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45691</v>
+        <v>45695</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>VAT Payable</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1519.21</v>
+        <v>3113.62</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -680,33 +680,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1885</v>
+        <v>2510</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45691</v>
+        <v>45702</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2634.21</v>
+        <v>906</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -714,33 +714,33 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1886</v>
+        <v>2517</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45691</v>
+        <v>45702</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1519.21</v>
+        <v>906</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -748,92 +748,92 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2248</v>
+        <v>2613</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45699</v>
+        <v>45706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1626.07</v>
       </c>
       <c r="H10" t="n">
-        <v>809.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2306</v>
+        <v>2679</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45699</v>
+        <v>45706</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1626.07</v>
       </c>
       <c r="H11" t="n">
-        <v>809.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2734</v>
+        <v>2775</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1493.37</v>
+        <v>4417.74</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -850,24 +850,24 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2767</v>
+        <v>2828</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1493.37</v>
+        <v>4417.74</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -884,24 +884,24 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2894</v>
+        <v>2988</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45709</v>
+        <v>45713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1125.5</v>
+        <v>2771.08</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -918,24 +918,24 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2905</v>
+        <v>3040</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45709</v>
+        <v>45713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1125.5</v>
+        <v>2771.08</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -952,24 +952,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3101</v>
+        <v>3219</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45714</v>
+        <v>45716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -978,27 +978,27 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>389.49</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3117</v>
+        <v>3224</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45714</v>
+        <v>45716</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1008,22 +1008,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>389.49</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3226</v>
+        <v>3820</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45716</v>
+        <v>45728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1049,15 +1049,15 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>20000</v>
+        <v>6467.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3231</v>
+        <v>3870</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45716</v>
+        <v>45728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1066,46 +1066,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>20000</v>
+        <v>6467.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3914</v>
+        <v>4124</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45729</v>
+        <v>45734</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1117,29 +1117,29 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>751.04</v>
+        <v>15132.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3953</v>
+        <v>4155</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45729</v>
+        <v>45734</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1151,29 +1151,29 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>751.04</v>
+        <v>15132.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4332</v>
+        <v>4512</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1182,32 +1182,32 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>43.24</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>173.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4355</v>
+        <v>4516</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1216,27 +1216,27 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>43.24</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>173.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4686</v>
+        <v>4693</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1250,27 +1250,27 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2570.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2802.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4732</v>
+        <v>4724</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1284,32 +1284,32 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2570.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2802.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4878</v>
+        <v>5054</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3260.24</v>
+        <v>1614.31</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1326,24 +1326,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4886</v>
+        <v>5089</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3260.24</v>
+        <v>1614.31</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1360,24 +1360,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4905</v>
+        <v>6988</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45749</v>
+        <v>45789</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1389,29 +1389,29 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>773.02</v>
+        <v>4947.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4961</v>
+        <v>7060</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45749</v>
+        <v>45789</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1423,24 +1423,24 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>773.02</v>
+        <v>4947.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5344</v>
+        <v>7259</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45757</v>
+        <v>45792</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1450,31 +1450,31 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2676.93</v>
+        <v>944.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5395</v>
+        <v>7298</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45757</v>
+        <v>45792</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1484,36 +1484,36 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2676.93</v>
+        <v>944.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5459</v>
+        <v>7945</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45758</v>
+        <v>45805</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1522,32 +1522,32 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2339.18</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>10964.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5473</v>
+        <v>7992</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45758</v>
+        <v>45805</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1556,22 +1556,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2339.18</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>10964.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6178</v>
+        <v>8025</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45772</v>
+        <v>45806</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1581,31 +1581,31 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2435.66</v>
+        <v>2318.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6206</v>
+        <v>8073</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45772</v>
+        <v>45806</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1615,61 +1615,61 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2435.66</v>
+        <v>2318.88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6574</v>
+        <v>8648</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45779</v>
+        <v>45818</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1226.68</v>
+        <v>907.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6595</v>
+        <v>8693</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45779</v>
+        <v>45818</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1692,61 +1692,61 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4130.37</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>907.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6602</v>
+        <v>8826</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45779</v>
+        <v>45820</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1226.68</v>
+        <v>594.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6603</v>
+        <v>8862</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45779</v>
+        <v>45820</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1760,86 +1760,86 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4130.37</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>594.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7342</v>
+        <v>9341</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45793</v>
+        <v>45828</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1860.22</v>
+        <v>1663.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7369</v>
+        <v>9361</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45793</v>
+        <v>45828</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1860.22</v>
+        <v>1663.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7497</v>
+        <v>9806</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45797</v>
+        <v>45838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1848,46 +1848,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>928.41</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>8362.700000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7519</v>
+        <v>9811</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45797</v>
+        <v>45838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>928.41</v>
+        <v>337.77</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1904,19 +1904,19 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7654</v>
+        <v>9854</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45799</v>
+        <v>45838</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1926,31 +1926,31 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>337.77</v>
       </c>
       <c r="H44" t="n">
-        <v>565.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7672</v>
+        <v>9855</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45799</v>
+        <v>45838</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1967,29 +1967,29 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>565.12</v>
+        <v>8362.700000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9105</v>
+        <v>10475</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45825</v>
+        <v>45849</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2001,58 +2001,58 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2214.72</v>
+        <v>1961.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9109</v>
+        <v>10516</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45825</v>
+        <v>45849</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3202.04</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1961.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>9145</v>
+        <v>11107</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45825</v>
+        <v>45861</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2066,18 +2066,18 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>604.95</v>
       </c>
       <c r="H48" t="n">
-        <v>2214.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9146</v>
+        <v>11128</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45825</v>
+        <v>45861</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3202.04</v>
+        <v>604.95</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2108,14 +2108,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9226</v>
+        <v>11419</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45827</v>
+        <v>45867</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2137,63 +2137,63 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1123.08</v>
+        <v>647.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9289</v>
+        <v>11450</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45827</v>
+        <v>45867</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>10978.46</v>
+        <v>647.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9299</v>
+        <v>11619</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45827</v>
+        <v>45870</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2205,15 +2205,15 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>10978.46</v>
+        <v>1023.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9300</v>
+        <v>11671</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45827</v>
+        <v>45870</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2222,46 +2222,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1123.08</v>
+        <v>1023.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9767</v>
+        <v>12196</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45835</v>
+        <v>45881</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2270,32 +2270,32 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1839.22</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>3003.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9783</v>
+        <v>12223</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45835</v>
+        <v>45881</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2304,41 +2304,41 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1839.22</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3003.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>9954</v>
+        <v>12248</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45840</v>
+        <v>45882</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>192.22</v>
+        <v>2016.05</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2346,33 +2346,33 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>9995</v>
+        <v>12293</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45840</v>
+        <v>45882</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>192.22</v>
+        <v>2016.05</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2380,53 +2380,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10188</v>
+        <v>12463</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45845</v>
+        <v>45887</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>4410.91</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>514.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10200</v>
+        <v>12503</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45845</v>
+        <v>45887</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2436,36 +2436,36 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>20152.14</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>514.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10230</v>
+        <v>12961</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45845</v>
+        <v>45896</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>20152.14</v>
+        <v>591.79</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2482,14 +2482,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10231</v>
+        <v>13034</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45845</v>
+        <v>45896</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>4410.91</v>
+        <v>591.79</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10348</v>
+        <v>13086</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45847</v>
+        <v>45897</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5782.53</v>
+        <v>12539.65</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10375</v>
+        <v>13134</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45847</v>
+        <v>45897</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5782.53</v>
+        <v>12539.65</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2584,92 +2584,92 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>11091</v>
+        <v>13164</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45861</v>
+        <v>45898</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>282.85</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1733.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11143</v>
+        <v>13216</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45861</v>
+        <v>45898</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>282.85</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1733.74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12396</v>
+        <v>13397</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45884</v>
+        <v>45903</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>467.75</v>
+        <v>2044.94</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2686,24 +2686,24 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12450</v>
+        <v>13461</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45884</v>
+        <v>45903</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>467.75</v>
+        <v>2044.94</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13121</v>
+        <v>13988</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45897</v>
+        <v>45912</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2732,32 +2732,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>6277.59</v>
       </c>
       <c r="H68" t="n">
-        <v>40886.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13146</v>
+        <v>14013</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45897</v>
+        <v>45912</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2766,46 +2766,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>6277.59</v>
       </c>
       <c r="H69" t="n">
-        <v>40886.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>14344</v>
+        <v>14203</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2817,29 +2817,29 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2313.88</v>
+        <v>387.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14348</v>
+        <v>14256</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2851,29 +2851,29 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2313.88</v>
+        <v>387.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>15237</v>
+        <v>14673</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45936</v>
+        <v>45925</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2882,32 +2882,32 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>134.79</v>
       </c>
       <c r="H72" t="n">
-        <v>5563.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>15263</v>
+        <v>14715</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45936</v>
+        <v>45925</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2916,100 +2916,100 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>134.79</v>
       </c>
       <c r="H73" t="n">
-        <v>5563.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15620</v>
+        <v>15171</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45943</v>
+        <v>45936</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>50000</v>
+        <v>4588.18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15674</v>
+        <v>15256</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45943</v>
+        <v>45936</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>50000</v>
+        <v>4588.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15754</v>
+        <v>15956</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3018,32 +3018,32 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>6724.4</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>763.54</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>15759</v>
+        <v>16032</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Director fees</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3052,18 +3052,18 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>6724.4</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>763.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15821</v>
+        <v>16069</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3089,15 +3089,15 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>3604.25</v>
+        <v>2849.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>15826</v>
+        <v>16115</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Customer receipt</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3123,216 +3123,216 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>3604.25</v>
+        <v>2849.72</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>15963</v>
+        <v>16268</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45950</v>
+        <v>45953</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>15448.03</v>
       </c>
       <c r="H80" t="n">
-        <v>763.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>16039</v>
+        <v>16272</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45950</v>
+        <v>45953</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>15448.03</v>
       </c>
       <c r="H81" t="n">
-        <v>763.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>16151</v>
+        <v>16412</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45952</v>
+        <v>45957</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>436.18</v>
       </c>
       <c r="H82" t="n">
-        <v>383.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>16197</v>
+        <v>16436</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45952</v>
+        <v>45957</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>436.18</v>
       </c>
       <c r="H83" t="n">
-        <v>383.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>16396</v>
+        <v>16520</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>303.23</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>2192.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16444</v>
+        <v>16535</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Payroll Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Staff travel claim</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>303.23</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>2192.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>16639</v>
+        <v>16625</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>45960</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1022.7</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>16702</v>
+        <v>16628</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1022.7</v>
+        <v>1326.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17115</v>
+        <v>16696</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45968</v>
+        <v>45960</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3429,63 +3429,63 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>4889.26</v>
+        <v>477</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17186</v>
+        <v>16697</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45968</v>
+        <v>45960</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>4889.26</v>
+        <v>1326.46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>18039</v>
+        <v>16938</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45986</v>
+        <v>45965</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3494,32 +3494,32 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>310.21</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2347.98</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>18093</v>
+        <v>16949</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45986</v>
+        <v>45965</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cost of Sales</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3528,18 +3528,18 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>310.21</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2347.98</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>18118</v>
+        <v>17147</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45987</v>
+        <v>45968</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3562,18 +3562,18 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>12106.86</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1988.41</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>18152</v>
+        <v>17184</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45987</v>
+        <v>45968</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3596,27 +3596,27 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>12106.86</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1988.41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18252</v>
+        <v>17384</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45989</v>
+        <v>45973</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3626,11 +3626,11 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>3704.02</v>
+        <v>2839.89</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3638,19 +3638,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>18295</v>
+        <v>17418</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45989</v>
+        <v>45973</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3660,11 +3660,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3704.02</v>
+        <v>2839.89</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3672,24 +3672,24 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18348</v>
+        <v>17452</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45992</v>
+        <v>45974</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3701,29 +3701,29 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>32707.19</v>
+        <v>22080.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>18380</v>
+        <v>17493</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45992</v>
+        <v>45974</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Payroll Expense</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3735,97 +3735,97 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>32707.19</v>
+        <v>22080.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>18699</v>
+        <v>17677</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45999</v>
+        <v>45979</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>11608.42</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2580.92</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>18759</v>
+        <v>17717</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45999</v>
+        <v>45979</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash at Bank</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>11608.42</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>2580.92</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>19151</v>
+        <v>19273</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3834,32 +3834,32 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>4733.96</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>195.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>19206</v>
+        <v>19280</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Staff travel claim</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3868,27 +3868,27 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>4733.96</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>195.95</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>19342</v>
+        <v>19775</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46009</v>
+        <v>46017</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3902,27 +3902,27 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>405.95</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>241.25</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>19348</v>
+        <v>19803</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46009</v>
+        <v>46017</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>405.95</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>241.25</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/idea_exports/Duplicate.xlsx
+++ b/fixtures/idea_exports/Duplicate.xlsx
@@ -2244,7 +2244,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>12196</v>
+        <v>12197</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>45881</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12223</v>
+        <v>12224</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>45881</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12248</v>
+        <v>12249</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>45882</v>
